--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2980004</v>
+        <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99156</v>
+        <v>99340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,37 +1478,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219875</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>jättetuja-beståndet, Öl</t>
+          <t>Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621410</v>
+        <v>621400</v>
       </c>
       <c r="R9" t="n">
-        <v>6346082</v>
+        <v>6346093</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,12 +1541,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2008-08-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2008-08-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,62 +1567,53 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson, Göran Wendt, Elna Hultqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Anders Carlberg, Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2980004</t>
+          <t>https://artportalen.se/Sighting/137099682</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3927047</v>
+        <v>2980004</v>
       </c>
       <c r="B10" t="n">
-        <v>102240</v>
+        <v>99156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>219875</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1683,51 +1693,51 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3927047</t>
+          <t>https://artportalen.se/Sighting/2980004</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6896697</v>
+        <v>3927047</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
+        <v>102240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tujabeståndet ost Skäftekärr, Öl</t>
+          <t>jättetuja-beståndet, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621390</v>
+        <v>621410</v>
       </c>
       <c r="R11" t="n">
-        <v>6346126</v>
+        <v>6346082</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1754,12 +1764,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
+          <t>2008-08-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
+          <t>2008-08-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,24 +1780,135 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Jan-Olof Petersson, Ulla-Britt Andersson, Göran Wendt, Elna Hultqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3927047</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6896697</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tujabeståndet ost Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>621390</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6346126</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-08-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-08-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6896697</t>
         </is>
@@ -1805,6 +1926,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1500,11 +1500,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skäftekärr, Öl</t>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31516-2026 artfynd.xlsx
+++ b/artfynd/A 31516-2026 artfynd.xlsx
@@ -1470,7 +1470,7 @@
         <v>137099682</v>
       </c>
       <c r="B9" t="n">
-        <v>99416</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
